--- a/artfynd/A 32744-2025 artfynd.xlsx
+++ b/artfynd/A 32744-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17208656</v>
+        <v>17208510</v>
       </c>
       <c r="B2" t="n">
-        <v>79764</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3929</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Läderskål</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Encoelia furfuracea</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Roth.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högberga 200 m vsv, Srm</t>
+          <t>Skebojvarn 500 m no, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598505.6190604334</v>
+        <v>598518</v>
       </c>
       <c r="R2" t="n">
-        <v>6548883.263786492</v>
+        <v>6548831</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,19 +753,9 @@
           <t>2015-03-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-03-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +767,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>MARKSLAG</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövdominerad åkerholme</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,56 +793,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17208610</v>
+        <v>125635457</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>220103</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högberga 200 m vsv, Srm</t>
+          <t>150 m V Högberga, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598505.6190604334</v>
+        <v>598523</v>
       </c>
       <c r="R3" t="n">
-        <v>6548883.263786492</v>
+        <v>6548911</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,255 +884,22 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hassellund</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Helena  Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Helena  Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>17208550</v>
-      </c>
-      <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Högberga 200 m vsv, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>598505.6190604334</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6548883.263786492</v>
-      </c>
-      <c r="S4" t="n">
-        <v>75</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Flen</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Helgesta</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2015-03-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2015-03-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>125635457</v>
-      </c>
-      <c r="B5" t="n">
-        <v>107310</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220103</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Klasefibbla</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Crepis praemorsa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Walther</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>150 m V Högberga, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>598523</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6548911</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Flen</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Helgesta</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Helena  Larsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Helena  Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32744-2025 artfynd.xlsx
+++ b/artfynd/A 32744-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17208510</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125635457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>